--- a/artfynd/A 27589-2023 artfynd.xlsx
+++ b/artfynd/A 27589-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 27589-2023 artfynd.xlsx
+++ b/artfynd/A 27589-2023 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>104711112</v>
       </c>
       <c r="B2" t="n">
-        <v>100516</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>102812</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -711,10 +706,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>699760.1033589563</v>
+        <v>699760</v>
       </c>
       <c r="R2" t="n">
-        <v>6344100.233804101</v>
+        <v>6344100</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -744,19 +739,9 @@
           <t>2001-05-24</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2001-05-24</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">

--- a/artfynd/A 27589-2023 artfynd.xlsx
+++ b/artfynd/A 27589-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>104711112</v>
       </c>
       <c r="B2" t="n">
-        <v>102812</v>
+        <v>102820</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 27589-2023 artfynd.xlsx
+++ b/artfynd/A 27589-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>104711112</v>
       </c>
       <c r="B2" t="n">
-        <v>102820</v>
+        <v>102830</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 27589-2023 artfynd.xlsx
+++ b/artfynd/A 27589-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>104711112</v>
       </c>
       <c r="B2" t="n">
-        <v>102830</v>
+        <v>102836</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 27589-2023 artfynd.xlsx
+++ b/artfynd/A 27589-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>104711112</v>
       </c>
       <c r="B2" t="n">
-        <v>102836</v>
+        <v>102837</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 27589-2023 artfynd.xlsx
+++ b/artfynd/A 27589-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>104711112</v>
       </c>
       <c r="B2" t="n">
-        <v>102837</v>
+        <v>102864</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 27589-2023 artfynd.xlsx
+++ b/artfynd/A 27589-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>104711112</v>
       </c>
       <c r="B2" t="n">
-        <v>102864</v>
+        <v>102870</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 27589-2023 artfynd.xlsx
+++ b/artfynd/A 27589-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>104711112</v>
       </c>
       <c r="B2" t="n">
-        <v>102870</v>
+        <v>102877</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 27589-2023 artfynd.xlsx
+++ b/artfynd/A 27589-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>104711112</v>
       </c>
       <c r="B2" t="n">
-        <v>102877</v>
+        <v>102881</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 27589-2023 artfynd.xlsx
+++ b/artfynd/A 27589-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>104711112</v>
       </c>
       <c r="B2" t="n">
-        <v>102881</v>
+        <v>102888</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 27589-2023 artfynd.xlsx
+++ b/artfynd/A 27589-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>104711112</v>
       </c>
       <c r="B2" t="n">
-        <v>102891</v>
+        <v>102896</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 27589-2023 artfynd.xlsx
+++ b/artfynd/A 27589-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>104711112</v>
       </c>
       <c r="B2" t="n">
-        <v>102896</v>
+        <v>102904</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 27589-2023 artfynd.xlsx
+++ b/artfynd/A 27589-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,41 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>104711112</v>
+        <v>104711123</v>
       </c>
       <c r="B2" t="n">
-        <v>102904</v>
+        <v>103683</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>CR</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>225046</v>
+        <v>222002</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vanlig skogsalm</t>
+          <t>Underviol</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Ulmus glabra subsp. glabra</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr"/>
+          <t>Viola mirabilis</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Havor 675 m NV, Gtl</t>
+          <t>Havor 700 m NV, Gtl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>699760</v>
+        <v>699601</v>
       </c>
       <c r="R2" t="n">
-        <v>6344100</v>
+        <v>6344038</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -746,7 +750,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Litet bestånd. Även km-ruta 41.</t>
+          <t>Spridd mot O. Även km-ruta 41.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -760,7 +764,7 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>Lövskog, frisk.</t>
+          <t>Lövridå mellan betad skog och åker.</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -775,6 +779,113 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr">
+        <is>
+          <t>Projekt Gotlands Flora</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>104711112</v>
+      </c>
+      <c r="B3" t="n">
+        <v>103404</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>225046</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Vanlig skogsalm</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Ulmus glabra subsp. glabra</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Havor 675 m NV, Gtl</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>699760</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6344100</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Havdhem</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2001-05-24</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2001-05-24</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Litet bestånd. Även km-ruta 41.</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>Lövskog, frisk.</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
         <is>
           <t>Projekt Gotlands Flora</t>
         </is>

--- a/artfynd/A 27589-2023 artfynd.xlsx
+++ b/artfynd/A 27589-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AZ3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -783,6 +788,11 @@
           <t>Projekt Gotlands Flora</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104711123</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -890,8 +900,17 @@
           <t>Projekt Gotlands Flora</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104711112</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>